--- a/data/trans_dic/P22$mutaSS-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,95</t>
+          <t>5,73; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,67</t>
+          <t>4,79; 9,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,59</t>
+          <t>4,89; 9,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,62</t>
+          <t>4,36; 8,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,33</t>
+          <t>4,71; 10,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,67</t>
+          <t>4,06; 10,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,41</t>
+          <t>3,7; 8,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,62</t>
+          <t>5,83; 9,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,52</t>
+          <t>5,92; 9,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,74</t>
+          <t>5,07; 8,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,74</t>
+          <t>5,02; 8,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,38</t>
+          <t>5,45; 8,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 15,37</t>
+          <t>8,37; 15,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,4</t>
+          <t>5,99; 12,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,82</t>
+          <t>3,61; 8,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 12,98</t>
+          <t>7,02; 12,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,87</t>
+          <t>3,18; 7,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,46</t>
+          <t>1,84; 6,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,55; 3,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,79</t>
+          <t>1,37; 3,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,38</t>
+          <t>6,32; 10,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,69</t>
+          <t>4,58; 8,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,37</t>
+          <t>2,3; 5,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,05</t>
+          <t>4,71; 8,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,89</t>
+          <t>0,67; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,56</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,31</t>
+          <t>0,19; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,94</t>
+          <t>1,2; 6,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,03</t>
+          <t>1,14; 5,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,8</t>
+          <t>0,27; 2,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,04</t>
+          <t>1,0; 3,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,13</t>
+          <t>0,68; 2,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,67</t>
+          <t>0,15; 1,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,87</t>
+          <t>0,06; 0,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,41</t>
+          <t>0,41; 1,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,31</t>
+          <t>0,38; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,12</t>
+          <t>0,69; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,89</t>
+          <t>1,48; 3,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,63</t>
+          <t>0,28; 1,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,89</t>
+          <t>0,46; 1,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,63</t>
+          <t>0,06; 0,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,04</t>
+          <t>0,93; 2,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,18</t>
+          <t>0,44; 1,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,76</t>
+          <t>0,71; 1,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,56</t>
+          <t>0,11; 0,66</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,15</t>
+          <t>0,91; 4,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,75</t>
+          <t>1,88; 4,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,67</t>
+          <t>0,29; 1,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,98</t>
+          <t>1,83; 4,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,18; 1,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,79</t>
+          <t>0,07; 0,75</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,1</t>
+          <t>1,74; 5,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,52</t>
+          <t>1,75; 6,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,1</t>
+          <t>0,33; 3,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,47</t>
+          <t>1,11; 10,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,87</t>
+          <t>1,86; 3,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,09</t>
+          <t>1,36; 3,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,46</t>
+          <t>0,37; 1,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,07</t>
+          <t>1,06; 3,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,77</t>
+          <t>2,09; 3,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,28</t>
+          <t>1,57; 3,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,49</t>
+          <t>0,47; 1,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,93</t>
+          <t>1,43; 3,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,25</t>
+          <t>2,94; 4,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,26</t>
+          <t>2,07; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,84</t>
+          <t>1,79; 2,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,4</t>
+          <t>1,97; 3,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,01</t>
+          <t>2,78; 4,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,67</t>
+          <t>1,65; 2,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,72</t>
+          <t>0,97; 1,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,15</t>
+          <t>1,3; 2,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,91</t>
+          <t>3,01; 3,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,79</t>
+          <t>1,98; 2,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,14</t>
+          <t>1,47; 2,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,62</t>
+          <t>1,82; 2,61</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27584; 51733</t>
+          <t>27057; 50793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20112; 42270</t>
+          <t>20951; 42623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22578; 45442</t>
+          <t>21000; 42605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21795; 43570</t>
+          <t>22041; 43710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14134; 31681</t>
+          <t>14438; 31976</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12676; 33540</t>
+          <t>12778; 31555</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13636; 32666</t>
+          <t>12846; 30898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25816; 43035</t>
+          <t>26084; 41730</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45686; 74127</t>
+          <t>46109; 74632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37872; 65679</t>
+          <t>38142; 67384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37936; 67841</t>
+          <t>38996; 67855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51905; 79824</t>
+          <t>51890; 79157</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30144; 56408</t>
+          <t>30709; 56492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24419; 51949</t>
+          <t>25094; 51132</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13713; 33200</t>
+          <t>13585; 31790</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31912; 58689</t>
+          <t>31739; 57719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11142; 29281</t>
+          <t>11810; 29097</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5934; 21850</t>
+          <t>6230; 23640</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2091; 12451</t>
+          <t>2066; 12466</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5549; 14517</t>
+          <t>5225; 14557</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46031; 76724</t>
+          <t>46693; 77139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34991; 65785</t>
+          <t>34641; 67229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18351; 40190</t>
+          <t>17248; 38531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39523; 67219</t>
+          <t>39290; 67578</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3717; 15660</t>
+          <t>3643; 14759</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>981; 9843</t>
+          <t>1038; 9153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1012; 12069</t>
+          <t>971; 10436</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5261</t>
+          <t>0; 6357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2040; 11650</t>
+          <t>2010; 11567</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2936; 13093</t>
+          <t>2977; 13557</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 4317</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>456; 4669</t>
+          <t>456; 4577</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7538; 21595</t>
+          <t>7066; 22410</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5802; 18957</t>
+          <t>6033; 19668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1030; 11524</t>
+          <t>1017; 11569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>395; 7226</t>
+          <t>461; 6989</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4566; 17386</t>
+          <t>5087; 17535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3848; 15146</t>
+          <t>4354; 15613</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8029; 24295</t>
+          <t>7904; 24720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 9687</t>
+          <t>0; 10250</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10938; 27786</t>
+          <t>10563; 27199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2043; 12505</t>
+          <t>2112; 12970</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3140; 15524</t>
+          <t>3787; 15170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>644; 6154</t>
+          <t>634; 6423</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18190; 39679</t>
+          <t>18044; 39041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8036; 22718</t>
+          <t>8439; 23430</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14484; 34771</t>
+          <t>13943; 35522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1834; 11196</t>
+          <t>2162; 13272</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3674; 14561</t>
+          <t>3174; 14385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6324</t>
+          <t>0; 5962</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7520</t>
+          <t>0; 7372</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 9065</t>
+          <t>0; 9500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9098; 27039</t>
+          <t>10716; 27625</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2179; 12701</t>
+          <t>2211; 13230</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7283</t>
+          <t>0; 6799</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3837</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15740; 36551</t>
+          <t>16852; 39027</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2370; 14349</t>
+          <t>2293; 14393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1016; 10840</t>
+          <t>1129; 11020</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1005; 10434</t>
+          <t>978; 9798</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5475; 18135</t>
+          <t>5180; 17236</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4747; 17410</t>
+          <t>4672; 17993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1046; 8900</t>
+          <t>958; 9607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2514; 25170</t>
+          <t>2681; 25511</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24575; 48269</t>
+          <t>23238; 45786</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14669; 34230</t>
+          <t>15080; 34550</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4020; 15751</t>
+          <t>3953; 16016</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8652; 23397</t>
+          <t>8093; 24029</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32442; 58247</t>
+          <t>32237; 58615</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22037; 45132</t>
+          <t>21603; 45228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6817; 20388</t>
+          <t>6387; 20825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13751; 39410</t>
+          <t>14350; 38929</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>97276; 138712</t>
+          <t>95956; 139631</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>71166; 111608</t>
+          <t>70850; 112598</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60264; 96076</t>
+          <t>60545; 96515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66788; 114636</t>
+          <t>66598; 117005</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92702; 135363</t>
+          <t>93862; 136370</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57818; 94649</t>
+          <t>58629; 93116</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33417; 60694</t>
+          <t>34190; 60778</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>46487; 76842</t>
+          <t>46305; 75605</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>200416; 259536</t>
+          <t>200005; 257203</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139991; 194149</t>
+          <t>137802; 194241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102501; 147543</t>
+          <t>101710; 146191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>127054; 182406</t>
+          <t>126269; 181596</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutaSS-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,76</t>
+          <t>5,96; 11,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,75</t>
+          <t>4,68; 9,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,93</t>
+          <t>5,09; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,65</t>
+          <t>4,19; 8,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,43</t>
+          <t>4,36; 10,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,03</t>
+          <t>3,95; 10,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,9</t>
+          <t>4,04; 9,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,33</t>
+          <t>5,4; 9,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,58</t>
+          <t>6,0; 9,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,96</t>
+          <t>4,85; 8,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,74</t>
+          <t>5,18; 8,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,31</t>
+          <t>5,29; 8,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 15,4</t>
+          <t>8,17; 15,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,21</t>
+          <t>5,94; 12,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,45</t>
+          <t>3,76; 8,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 12,76</t>
+          <t>6,75; 12,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,82</t>
+          <t>2,99; 7,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,99</t>
+          <t>1,91; 6,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,35</t>
+          <t>0,55; 3,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,8</t>
+          <t>1,43; 3,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,44</t>
+          <t>6,4; 10,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,88</t>
+          <t>4,62; 8,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,15</t>
+          <t>2,45; 5,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,1</t>
+          <t>4,57; 7,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,73</t>
+          <t>0,67; 2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,0</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,89</t>
+          <t>1,19; 6,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,21</t>
+          <t>1,16; 5,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,74</t>
+          <t>0,26; 2,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,16</t>
+          <t>1,05; 2,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,21</t>
+          <t>0,59; 2,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,68</t>
+          <t>0,15; 1,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,84</t>
+          <t>0,16; 1,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,42</t>
+          <t>0,41; 1,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,35</t>
+          <t>0,33; 1,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,15</t>
+          <t>0,74; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,81</t>
+          <t>1,52; 3,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,69</t>
+          <t>0,27; 1,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,84</t>
+          <t>0,41; 1,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,66</t>
+          <t>0,12; 0,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,0</t>
+          <t>0,98; 2,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,22</t>
+          <t>0,45; 1,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,8</t>
+          <t>0,72; 1,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,66</t>
+          <t>0,11; 0,56</t>
         </is>
       </c>
     </row>
@@ -1224,39 +1224,39 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,1</t>
+          <t>1,04; 3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,86</t>
+          <t>1,8; 5,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,29; 1,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,25</t>
+          <t>1,75; 4,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,13</t>
+          <t>0,19; 1,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,14 +1332,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,75</t>
+          <t>0,07; 0,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,8</t>
+          <t>1,77; 6,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,74</t>
+          <t>1,75; 6,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,35</t>
+          <t>0,37; 3,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,61</t>
+          <t>1,17; 8,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,67</t>
+          <t>1,84; 3,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,11</t>
+          <t>1,33; 3,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,48</t>
+          <t>0,37; 1,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,16</t>
+          <t>0,94; 2,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,8</t>
+          <t>2,07; 3,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,29</t>
+          <t>1,6; 3,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,52</t>
+          <t>0,44; 1,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,89</t>
+          <t>1,25; 3,33</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,28</t>
+          <t>2,93; 4,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,29</t>
+          <t>2,08; 3,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,85</t>
+          <t>1,78; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,47</t>
+          <t>2,13; 3,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,04</t>
+          <t>2,75; 3,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,62</t>
+          <t>1,62; 2,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,72</t>
+          <t>0,95; 1,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,11</t>
+          <t>1,38; 2,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,87</t>
+          <t>3,03; 3,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,79</t>
+          <t>1,96; 2,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,12</t>
+          <t>1,47; 2,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,61</t>
+          <t>1,88; 2,57</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>32944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64203</t>
+          <t>67949</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27057; 50793</t>
+          <t>28134; 53803</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20951; 42623</t>
+          <t>20444; 42216</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21000; 42605</t>
+          <t>21821; 43769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22041; 43710</t>
+          <t>23081; 46936</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14438; 31976</t>
+          <t>13361; 30940</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12778; 31555</t>
+          <t>12425; 32406</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12846; 30898</t>
+          <t>14010; 32754</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26084; 41730</t>
+          <t>26391; 45041</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46109; 74632</t>
+          <t>46701; 75596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38142; 67384</t>
+          <t>36455; 66223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38996; 67855</t>
+          <t>40184; 68992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51890; 79157</t>
+          <t>54989; 84242</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42946</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>54029</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30709; 56492</t>
+          <t>29966; 55361</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25094; 51132</t>
+          <t>24881; 50552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13585; 31790</t>
+          <t>14143; 32373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31739; 57719</t>
+          <t>32637; 59027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11810; 29097</t>
+          <t>11128; 29258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6230; 23640</t>
+          <t>6472; 21826</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2066; 12466</t>
+          <t>2047; 13236</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5225; 14557</t>
+          <t>6070; 16229</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46693; 77139</t>
+          <t>47290; 79370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34641; 67229</t>
+          <t>35002; 65937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17248; 38531</t>
+          <t>18336; 40657</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39290; 67578</t>
+          <t>41453; 71212</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2822</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3643; 14759</t>
+          <t>3620; 14555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1038; 9153</t>
+          <t>987; 9358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971; 10436</t>
+          <t>965; 9370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6357</t>
+          <t>0; 6289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2010; 11567</t>
+          <t>1996; 11718</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2977; 13557</t>
+          <t>3016; 13372</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4317</t>
+          <t>0; 5309</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>456; 4577</t>
+          <t>487; 4888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7066; 22410</t>
+          <t>7430; 21081</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6033; 19668</t>
+          <t>5223; 18732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1017; 11569</t>
+          <t>1032; 11638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>461; 6989</t>
+          <t>1031; 7394</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5440</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5087; 17535</t>
+          <t>5057; 17647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4354; 15613</t>
+          <t>3835; 15248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7904; 24720</t>
+          <t>8512; 25211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10250</t>
+          <t>0; 9028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10563; 27199</t>
+          <t>10827; 27383</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2112; 12970</t>
+          <t>2062; 13066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3787; 15170</t>
+          <t>3352; 14219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>634; 6423</t>
+          <t>1021; 6552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18044; 39041</t>
+          <t>19036; 40069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8439; 23430</t>
+          <t>8604; 23075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13943; 35522</t>
+          <t>14235; 34303</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2162; 13272</t>
+          <t>2172; 11134</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3506</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3174; 14385</t>
+          <t>3639; 13715</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5962</t>
+          <t>0; 5285</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7372</t>
+          <t>0; 7971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 9500</t>
+          <t>0; 8630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10716; 27625</t>
+          <t>10264; 28571</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2211; 13230</t>
+          <t>2174; 12269</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6799</t>
+          <t>0; 7899</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3898</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16852; 39027</t>
+          <t>16048; 38092</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2293; 14393</t>
+          <t>2365; 14147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1129; 11020</t>
+          <t>1135; 10981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>978; 9798</t>
+          <t>1039; 10829</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>21524</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5180; 17236</t>
+          <t>5256; 18397</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4672; 17993</t>
+          <t>4676; 18247</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>958; 9607</t>
+          <t>1055; 9583</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2681; 25511</t>
+          <t>2778; 21076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23238; 45786</t>
+          <t>22900; 44672</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15080; 34550</t>
+          <t>14783; 34379</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3953; 16016</t>
+          <t>3990; 15810</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8093; 24029</t>
+          <t>7956; 19364</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32237; 58615</t>
+          <t>31983; 58933</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21603; 45228</t>
+          <t>21957; 46813</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6387; 20825</t>
+          <t>6064; 21324</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14350; 38929</t>
+          <t>13518; 35999</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>91833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>61725</t>
+          <t>63436</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>152184</t>
+          <t>155269</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>95956; 139631</t>
+          <t>95469; 139372</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>70850; 112598</t>
+          <t>71128; 112309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60545; 96515</t>
+          <t>60373; 97123</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66598; 117005</t>
+          <t>73377; 114699</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93862; 136370</t>
+          <t>92736; 133525</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58629; 93116</t>
+          <t>57457; 94306</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34190; 60778</t>
+          <t>33526; 61902</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>46305; 75605</t>
+          <t>50276; 76300</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>200005; 257203</t>
+          <t>201353; 262067</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>137802; 194241</t>
+          <t>136585; 191866</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101710; 146191</t>
+          <t>101889; 147886</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>126269; 181596</t>
+          <t>132700; 182217</t>
         </is>
       </c>
     </row>
